--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,6 +1118,132 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135936101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136888553</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334747</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6387144</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136888553</t>
         </is>
       </c>
     </row>
@@ -1127,6 +1253,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,48 +904,72 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105373755</v>
+        <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100034</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mattjärnen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334822</v>
+        <v>334747</v>
       </c>
       <c r="R4" t="n">
-        <v>6387102</v>
+        <v>6387144</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +993,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög förbi mossparti vid tjärnen samt jagade änder i mossen. Troligen sträckande fågel.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,27 +1028,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105373755</t>
+          <t>https://artportalen.se/Sighting/136891333</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135936101</v>
+        <v>105373755</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,17 +1076,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granndalen, Granndalen, Hl</t>
+          <t>Mattjärnen, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334570</v>
+        <v>334822</v>
       </c>
       <c r="R5" t="n">
-        <v>6387032</v>
+        <v>6387102</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,27 +1110,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:35</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spår av spillkråka</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,27 +1130,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135936101</t>
+          <t>https://artportalen.se/Sighting/105373755</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136888553</v>
+        <v>135936101</v>
       </c>
       <c r="B6" t="n">
-        <v>57195</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,51 +1158,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+          <t>Granndalen, Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334747</v>
+        <v>334570</v>
       </c>
       <c r="R6" t="n">
-        <v>6387144</v>
+        <v>6387032</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1212,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spår av spillkråka</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,6 +1257,132 @@
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135936101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136888553</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6387144</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136888553</t>
         </is>
@@ -1254,6 +1395,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57934</v>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Mats Foss, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
         <v>136888553</v>
       </c>
       <c r="B7" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57947</v>
+        <v>57949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>136888553</v>
       </c>
       <c r="B7" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -937,21 +937,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1297,16 +1285,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57949</v>
+        <v>57959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>136888553</v>
       </c>
       <c r="B7" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57959</v>
+        <v>57960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>136888553</v>
       </c>
       <c r="B7" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57960</v>
+        <v>57961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 393-2025 artfynd.xlsx
+++ b/artfynd/A 393-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>136891333</v>
       </c>
       <c r="B4" t="n">
-        <v>57961</v>
+        <v>57964</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
